--- a/docs/architecture/v2-draft-wording-review.xlsx
+++ b/docs/architecture/v2-draft-wording-review.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRS105 wording" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRS105 lines" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRS105 map" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Size thresholds" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -65,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -74,6 +75,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -484,17 +488,24 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Size thresholds (added 2026-10-20, DEC-066): the 'Size thresholds' sheet lists the draft company-law limits the size test reads, one row per set and class. Check each figure, the dates each set governs and the 'prior year on first year' transitional rule against the instrument named, then set a Verdict on the MICRO row of each set. Each set is imported UNVERIFIED and verified in the platform like a standard version.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>FRS102-1A-SMALL-DRAFT: FRS 102 The Financial Reporting Standard applicable in the UK and Republic of Ireland - Section 1A Small Entities - FRS 102 Section 1A small entity - engineering draft 0.1 (unverified). 22 wording rules, 33 statement lines, 18 map entries.</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FRS102-1A-SMALL-DRAFT: FRS 102 The Financial Reporting Standard applicable in the UK and Republic of Ireland - Section 1A Small Entities - FRS 102 Section 1A small entity - engineering draft 0.1 (unverified). 22 wording rules, 33 statement lines, 18 map entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>FRS105-MICRO-DRAFT: FRS 105 The Financial Reporting Standard applicable to the Micro-entities Regime - FRS 105 micro-entity - engineering draft 0.1 (unverified). 6 wording rules, 23 statement lines, 20 map entries.</t>
         </is>
@@ -4383,4 +4394,319 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Governs years beginning</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Prior year on first year</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Turnover</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Balance-sheet total</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Average employees</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Note for the verifier</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Companies Act 2006 size thresholds from 2016 - engineering draft 0.1 (unverified)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2016-01-01 to 2025-04-05</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>MICRO</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>632000</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>316000</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Companies Act 2006 ss.382, 384A and 465 as amended by SI 2015/980. Drafted, not retrieved: check every figure against the text in force (https://www.legislation.gov.uk/uksi/2015/980/contents)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Check the six money limits and the three employee limits against ss.382(3), 384A(4) and 465(3) as amended by SI 2015/980. priorYearOnFirst is set because engineering understands the 2015 regulations let a company apply the new thresholds to the preceding year when testing the first year they govern: confirm the transitional provision and its wording, or set it to false.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Companies Act 2006 size thresholds from 2016 - engineering draft 0.1 (unverified)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2016-01-01 to 2025-04-05</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>SMALL</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>10200000</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Companies Act 2006 size thresholds from 2016 - engineering draft 0.1 (unverified)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2016-01-01 to 2025-04-05</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Companies Act 2006 size thresholds from 6 April 2025 - engineering draft 0.1 (unverified)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-06 to open</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>MICRO</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Companies Act 2006 ss.382, 384A and 465 as amended by the Companies (Accounts and Reports) (Amendment and Transitional Provision) Regulations 2024 (SI 2024/1303). Drafted, not retrieved: check every figure against the text in force (https://www.legislation.gov.uk/uksi/2024/1303/contents)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Check the limits against ss.382(3), 384A(4) and 465(3) as amended by SI 2024/1303, and the commencement date. priorYearOnFirst is set because engineering understands the transitional provision of SI 2024/1303 lets a company apply the new thresholds to the preceding financial year when testing the first year beginning on or after 6 April 2025: confirm, or set it to false. LLPs have their own regulations and are not covered by this set.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Companies Act 2006 size thresholds from 6 April 2025 - engineering draft 0.1 (unverified)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-06 to open</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>SMALL</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Companies Act 2006 size thresholds from 6 April 2025 - engineering draft 0.1 (unverified)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-06 to open</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>27000000</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="J2:J7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Agree,Change,Remove"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/architecture/v2-draft-wording-review.xlsx
+++ b/docs/architecture/v2-draft-wording-review.xlsx
@@ -500,14 +500,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FRS102-1A-SMALL-DRAFT: FRS 102 The Financial Reporting Standard applicable in the UK and Republic of Ireland - Section 1A Small Entities - FRS 102 Section 1A small entity - engineering draft 0.1 (unverified). 22 wording rules, 33 statement lines, 18 map entries.</t>
+          <t>FRS102-1A-SMALL-DRAFT: FRS 102 The Financial Reporting Standard applicable in the UK and Republic of Ireland - Section 1A Small Entities - FRS 102 Section 1A small entity - engineering draft 0.2 (unverified). 22 wording rules, 33 statement lines, 18 map entries.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FRS105-MICRO-DRAFT: FRS 105 The Financial Reporting Standard applicable to the Micro-entities Regime - FRS 105 micro-entity - engineering draft 0.1 (unverified). 6 wording rules, 23 statement lines, 20 map entries.</t>
+          <t>FRS105-MICRO-DRAFT: FRS 105 The Financial Reporting Standard applicable to the Micro-entities Regime - FRS 105 micro-entity - engineering draft 0.2 (unverified). 6 wording rules, 23 statement lines, 20 map entries.</t>
         </is>
       </c>
     </row>
@@ -814,17 +814,18 @@
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>The company has only basic financial instruments. Trade and other debtors and creditors, cash and bank balances, and loans are measured at transaction price and subsequently at amortised cost.</t>
+          <t>Basic financial instruments (trade and other debtors and creditors, cash and bank balances, and loans) are measured at transaction price and subsequently at amortised cost.
+{{fact:text.otherFinancialInstruments}}</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>FRS 102 Section 11 (basic financial instruments)</t>
+          <t>FRS 102 Section 11 (basic financial instruments); Section 12 (other financial instruments)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Only right where the company has no other financial instruments (Section 12). Check the measurement wording, including for loans on non-market terms.</t>
+          <t>The policy no longer asserts that the company has only basic financial instruments (DEC-072 F3): the preparer states the position in text.otherFinancialInstruments, for example "The company has no other financial instruments." or the policy for those it has (Section 12). Check the measurement wording, including for loans on non-market terms.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -894,7 +895,7 @@
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>The average number of persons employed by the company (including directors) during the year was {{fact:employees.average}} ({{year:priorEnd}}: {{fact:employees.averagePrior}}).</t>
+          <t>The average number of persons employed by the company during the year was {{fact:employees.average}} ({{year:priorEnd}}: {{fact:employees.averagePrior}}).</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -904,7 +905,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Confirm whether directors are included in the count.</t>
+          <t>s.411(5)-(6) counts the persons employed under contracts of service; a director is counted only if employed under one, so the wording no longer says "(including directors)" (DEC-072 F2). If the firm wants to state whether directors are included, add it before verifying.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1026,18 +1027,19 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Amounts falling due after more than one year: {{line:B.CA1}} ({{year:priorEnd}}: {{line:B.CA1:prior}}).
-{{fact:text.securedDebts}}</t>
+          <t>Creditors falling due after more than one year: {{line:B.CA1}} ({{year:priorEnd}}: {{line:B.CA1:prior}}).
+Debts payable, or repayable by instalments, after more than five years from the balance sheet date: {{fact:text.debtsAfterFiveYears}}
+Debts on which security has been given, and the nature of the security: {{fact:text.securedDebts}}</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>SI 2008/409 Sch 1 (indebtedness: amounts due after five years, security given)</t>
+          <t>SI 2008/409 Sch 1 (details of indebtedness: debts payable after more than five years; debts on which security is given and its nature)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>text.securedDebts gives the amounts payable after five years and the security given, or says there are none.</t>
+          <t>The required disclosure is the debts payable after more than FIVE years and the secured debts with the nature of the security, not the after-one-year figure (DEC-072 F1). The one-year line stays for context and so that the note is left out when there are no such creditors. text.debtsAfterFiveYears gives the amount (or none) and text.securedDebts the secured debts and the security (or none). Confirm the paragraph of Sch 1 and whether instalment debts are stated separately.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -3044,7 +3046,7 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>The average number of persons employed by the company (including directors) during the year was {{fact:employees.average}} ({{year:priorEnd}}: {{fact:employees.averagePrior}}).</t>
+          <t>The average number of persons employed by the company during the year was {{fact:employees.average}} ({{year:priorEnd}}: {{fact:employees.averagePrior}}).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -3054,7 +3056,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Confirm the requirement applies to micro-entities for the periods in scope, and whether directors are counted.</t>
+          <t>Confirm the requirement applies to micro-entities for the periods in scope. s.411(5)-(6) counts the persons employed under contracts of service; a director is counted only if employed under one, so the wording no longer says "(including directors)" (DEC-072 F2). If the firm wants to state whether directors are included, add it before verifying.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
